--- a/model/data/invoice/sale-invoices-from-digikala/1405-03-30-sale-zibavash-express.xlsx
+++ b/model/data/invoice/sale-invoices-from-digikala/1405-03-30-sale-zibavash-express.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>شیوه ارسال مرسوله</t>
   </si>
@@ -128,6 +128,12 @@
   </si>
   <si>
     <t>09127579926</t>
+  </si>
+  <si>
+    <t>رژ مو گلدن رز مدل Brown | گارانتی اصالت و سلامت فیزیکی کالا</t>
+  </si>
+  <si>
+    <t>5ساعت</t>
   </si>
 </sst>
 </file>
@@ -652,13 +658,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1">
-        <v>756399</v>
+        <v>759485</v>
       </c>
       <c r="E3" s="1">
-        <v>33868475</v>
+        <v>33869152</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1">
@@ -668,16 +674,16 @@
         <v>365801251</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="K3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>5810000</v>
+        <v>6035900</v>
       </c>
       <c r="M3" s="1">
         <v>1390000</v>
